--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/env_coherence/taxa_env_class_counts.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
